--- a/round1/round1.xlsx
+++ b/round1/round1.xlsx
@@ -487,7 +487,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66113424</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -512,21 +512,21 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66113322</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -539,16 +539,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -560,12 +560,12 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66112233</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -578,16 +578,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>554</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -599,12 +599,12 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>594</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123456789</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -617,33 +617,33 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>464</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6611654</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -677,12 +677,12 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>654212</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -695,16 +695,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -716,12 +716,12 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>655454</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -755,12 +755,12 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2154545</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1548</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>41212</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>646</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -794,12 +794,12 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>43427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5464654</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>521541</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -833,12 +833,12 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>521589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>54654654654</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -851,16 +851,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>5412</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -872,12 +872,12 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>5438</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>456456</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -890,16 +890,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -911,12 +911,12 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4652</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -929,33 +929,33 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2121</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2416</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>34563</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -989,12 +989,12 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1007,16 +1007,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1132</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1028,12 +1028,12 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>456654</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5421512</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1067,12 +1067,12 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>5421746</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4654</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1085,16 +1085,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1106,12 +1106,12 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>54654</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>2121</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1145,12 +1145,12 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4654</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1163,16 +1163,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1184,12 +1184,12 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>45653</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1202,16 +1202,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
